--- a/registration_forms/042_pocket_pa_client_consultation_form--registration_forms.xlsx
+++ b/registration_forms/042_pocket_pa_client_consultation_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'email',_'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Email', 'value': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'phone',_'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Phone', 'value': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'monday',_'value':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Monday', 'value': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'tuesday',_'value':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Tuesday', 'value': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'wednesday',_'value':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Wednesday', 'value': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'thursday',_'value':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Thursday', 'value': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'friday',_'value':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Friday', 'value': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'15_minutes',_'value':_15}</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': '15 minutes', 'value': 15}</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'30_minutes',_'value':_30}</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': '30 minutes', 'value': 30}</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'45_minutes',_'value':_45}</t>
+          <t>45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': '45 minutes', 'value': 45}</t>
+          <t>45</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'60_minutes',_'value':_60}</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': '60 minutes', 'value': 60}</t>
+          <t>60</t>
         </is>
       </c>
     </row>
